--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11610" yWindow="1590" windowWidth="13590" windowHeight="11790" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mappings" sheetId="1" state="visible" r:id="rId1"/>
@@ -35,15 +35,21 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.5999938962981048"/>
+        <bgColor theme="4" tint="0.5999938962981048"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -66,15 +72,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,12 +560,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Potência Total_mean_mean_of_windows</t>
+          <t>Potência Total_mean_of_windows</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Potência Total_mean_sd_of_windows</t>
+          <t>Potência Total_sd_of_windows</t>
         </is>
       </c>
     </row>
@@ -584,12 +606,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T_CARTER_mean_mean_of_windows</t>
+          <t>T_CARTER_mean_of_windows</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T_CARTER_mean_sd_of_windows</t>
+          <t>T_CARTER_sd_of_windows</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -606,12 +628,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T_AMBIENTE_mean_mean_of_windows</t>
+          <t>T_AMBIENTE_mean_of_windows</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T_AMBIENTE_mean_sd_of_windows</t>
+          <t>T_AMBIENTE_sd_of_windows</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -635,6 +657,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="66" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="72.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="66" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="66.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="62.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="56.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="61.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="71.7109375" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="78.5703125" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="36.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="58.140625" bestFit="1" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1348,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1357,15 +1390,9 @@
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="10" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="36" customWidth="1" min="18" max="18"/>
@@ -1449,15 +1476,25 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>y_tol_plus</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>y_tol_minus</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>filter_h2o_list</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>label_variant</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1525,12 +1562,18 @@
       <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Legacy: nth with error bars</t>
         </is>
@@ -1589,12 +1632,18 @@
       <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Legacy: consumo with error bars</t>
         </is>
@@ -1648,12 +1697,18 @@
       <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Legacy: MFB_10_90</t>
         </is>
@@ -1707,12 +1762,18 @@
       <c r="L5" t="n">
         <v>5</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Legacy: Delta-T no labels</t>
         </is>
@@ -1766,17 +1827,23 @@
       <c r="L6" t="n">
         <v>5</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>box</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Legacy: labels box</t>
         </is>
@@ -1830,17 +1897,23 @@
       <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Legacy: labels tag</t>
         </is>
@@ -1894,17 +1967,23 @@
       <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>marker</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Legacy: labels marker</t>
         </is>
@@ -1958,17 +2037,23 @@
       <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>badge</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Legacy: labels badge</t>
         </is>
@@ -2022,12 +2107,18 @@
       <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Legacy: Air_kg_h</t>
         </is>
@@ -2081,12 +2172,18 @@
       <c r="L11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Legacy: Air_g_s</t>
         </is>
@@ -2140,12 +2237,18 @@
       <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Legacy: humidity</t>
         </is>
@@ -2199,12 +2302,18 @@
       <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Legacy: T_E_CIL_AVG</t>
         </is>
@@ -2258,12 +2367,18 @@
       <c r="L14" t="n">
         <v>5</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Legacy: Q_EVAP_NET vs power</t>
         </is>
@@ -2308,12 +2423,18 @@
           <t>Q_EVAP_NET (kW)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Legacy: Q_EVAP_NET vs Air_kg_h</t>
         </is>
@@ -2340,7 +2461,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P_COLETOR_RAW_mean_mean_of_windows</t>
+          <t>P_COLETOR_RAW_mean_of_windows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2358,12 +2479,18 @@
           <t>Q_EVAP_NET (kW)</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Legacy: Q_EVAP_NET vs P_COLETOR (will skip if col missing)</t>
         </is>
@@ -2380,7 +2507,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>raw_P_E_TURB_RAW_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_P_E_TURB_RAW_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2395,7 +2522,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>P_E_TURB_RAW_mean_mean_of_windows</t>
+          <t>P_E_TURB_RAW_mean_of_windows</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2417,12 +2544,18 @@
       <c r="L17" t="n">
         <v>5</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2439,7 +2572,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>raw_P_S_TURB_RAW_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_P_S_TURB_RAW_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2454,7 +2587,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>P_S_TURB_RAW_mean_mean_of_windows</t>
+          <t>P_S_TURB_RAW_mean_of_windows</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2476,12 +2609,18 @@
       <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2498,7 +2637,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>raw_P_E_COMP_RAW_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_P_E_COMP_RAW_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2513,7 +2652,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>P_E_COMP_RAW_mean_mean_of_windows</t>
+          <t>P_E_COMP_RAW_mean_of_windows</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2535,12 +2674,18 @@
       <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2557,7 +2702,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>raw_P_S_COMP_RAW_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_P_S_COMP_RAW_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2572,7 +2717,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>P_S_COMP_RAW_mean_mean_of_windows</t>
+          <t>P_S_COMP_RAW_mean_of_windows</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2594,12 +2739,18 @@
       <c r="L20" t="n">
         <v>5</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2616,7 +2767,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>raw_P_COLETOR_RAW_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_P_COLETOR_RAW_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2631,7 +2782,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>P_COLETOR_RAW_mean_mean_of_windows</t>
+          <t>P_COLETOR_RAW_mean_of_windows</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2653,12 +2804,18 @@
       <c r="L21" t="n">
         <v>5</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2675,7 +2832,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>raw_T_ADMISS_O_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_ADMISS_O_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2690,7 +2847,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>T_ADMISSÃO_mean_mean_of_windows</t>
+          <t>T_ADMISSÃO_mean_of_windows</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2712,12 +2869,18 @@
       <c r="L22" t="n">
         <v>5</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2734,7 +2897,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>raw_T_E_TURB_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_E_TURB_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2749,7 +2912,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>T_E_TURB_mean_mean_of_windows</t>
+          <t>T_E_TURB_mean_of_windows</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2771,12 +2934,18 @@
       <c r="L23" t="n">
         <v>5</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2793,7 +2962,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>raw_T_S_TURB_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_S_TURB_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2808,7 +2977,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>T_S_TURB_mean_mean_of_windows</t>
+          <t>T_S_TURB_mean_of_windows</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2830,12 +2999,18 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2852,7 +3027,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>raw_T_E_COMP_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_E_COMP_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2867,7 +3042,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>T_E_COMP_mean_mean_of_windows</t>
+          <t>T_E_COMP_mean_of_windows</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2889,12 +3064,18 @@
       <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2911,7 +3092,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>raw_T_S_COMP_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_S_COMP_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2926,7 +3107,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>T_S_COMP_mean_mean_of_windows</t>
+          <t>T_S_COMP_mean_of_windows</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2948,12 +3129,18 @@
       <c r="L26" t="n">
         <v>5</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -2970,7 +3157,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>raw_T_E_CIL_1_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_E_CIL_1_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2985,7 +3172,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>T_S_CIL_1_mean_mean_of_windows</t>
+          <t>T_S_CIL_1_mean_of_windows</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3007,12 +3194,18 @@
       <c r="L27" t="n">
         <v>5</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -3029,7 +3222,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>raw_T_E_CIL_2_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_E_CIL_2_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3044,7 +3237,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>T_S_CIL_2_mean_mean_of_windows</t>
+          <t>T_S_CIL_2_mean_of_windows</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3066,12 +3259,18 @@
       <c r="L28" t="n">
         <v>5</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -3088,7 +3287,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>raw_T_E_CIL_3_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_E_CIL_3_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3103,7 +3302,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>T_S_CIL_3_mean_mean_of_windows</t>
+          <t>T_S_CIL_3_mean_of_windows</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3125,12 +3324,18 @@
       <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -3147,7 +3352,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>raw_T_E_CIL_4_mean_mean_of_windows_vs_power_all.png</t>
+          <t>raw_T_E_CIL_4_mean_of_windows_vs_power_all.png</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3162,7 +3367,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>T_S_CIL_4_mean_mean_of_windows</t>
+          <t>T_S_CIL_4_mean_of_windows</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3184,12 +3389,18 @@
       <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Legacy: raw requested list</t>
         </is>
@@ -3233,14 +3444,763 @@
       <c r="L31" t="n">
         <v>5</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>6,25,35</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>AUTO: expand one plot per KIBOX_* column (except KIBOX_N_files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nox_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NOX vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NOX_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NOX</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Added: gas emissions via config (NOX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>co_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CO vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CO_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Added: gas emissions via config (CO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>co2_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CO2 vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CO2_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>55</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Added: gas emissions via config (CO2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>o2_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>O2 vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>O2_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>55</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Added: gas emissions via config (O2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ect_ctrl_error_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ECT control error (T_S_AGUA - DEM_TH2O) vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ECT_CTRL_ERROR_C</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Control error (degC)</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>55</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>ECT control stability with +/-2C tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bsfc_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Specific fuel consumption vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BSFC_g_kWh</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>U_BSFC_g_kWh</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Specific fuel consumption (g/kWh)</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>55</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>BSFC from Consumo_kg_h and power with propagated uncertainty from fuel and power channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>t_s_agua_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Engine Coolant temperature vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Temperature (°C)</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>55</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>80</v>
+      </c>
+      <c r="N38" t="n">
+        <v>90</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-87</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>t_watercooler_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER vs Load (all fuels)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Power command (kW)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER (degC)</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>55</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Added by request: temperature vs Load_kW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>t_radiador_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T_RADIADOR vs Load (all fuels)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Power command (kW)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>T_RADIADOR (degC)</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>55</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Added by request: temperature vs Load_kW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>t_carter_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>T_CARTER vs Load (all fuels)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>T_CARTER_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Power command (kW)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>T_CARTER (degC)</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>55</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Added by request: temperature vs Load_kW with uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>t_ambiente_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE vs Load (all fuels)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Power command (kW)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE (degC)</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>55</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Added by request: temperature vs Load_kW with uncertainty.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3329,6 +4289,26 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MAX_ECT_CONTROL_ERROR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Erro de controle se |T_S_AGUA - DEM_TH2O| exceder este limite (faixa +-2 degC).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -171,6 +171,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Diretorio varrido recursivamente para ler os arquivos LabVIEW/Kibox. Se vazio, usa raw\PROCESSAR ao lado do script. Aceita caminho absoluto ou relativo ao diretorio do script.</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Diretorio de saida do pipeline. Se vazio, usa out ao lado do script. Aceita caminho absoluto ou relativo ao diretorio do script.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1307,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,8 +1390,25 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RAW_INPUT_DIR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OUT_DIR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -4284,7 +4284,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>Motec_Exhaust Lambda_sd_of_windows</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Added by request: MoTeC exhaust lambda vs Load_kW with fixed lambda scale 0.90..1.10 step 0.02.</t>
+          <t>Added by request: MoTeC exhaust lambda vs Load_kW with SD-only uncertainty and fixed lambda scale 0.90..1.10 step 0.02.</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -1430,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T44"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4399,6 +4399,76 @@
       <c r="T44" t="inlineStr">
         <is>
           <t>Added by request: MoTeC ignition advance vs Load_kW with SD-only uncertainty and autoscale on Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>motec_fuel_closed_loop_trim_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MoTeC fuel closed loop trim vs Load (all fuels)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motec_Fuel Closed Loop Control Bank 1 Trim_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Motec_Fuel Closed Loop Control Bank 1 Trim_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Power command (kW)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Fuel closed loop trim bank 1 (%Trim)</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>55</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6,25,35</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Added by request: MoTeC fuel closed loop control bank 1 trim vs Load_kW with SD-only uncertainty and autoscale on Y.</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -4385,6 +4385,9 @@
       <c r="L44" t="n">
         <v>5</v>
       </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
@@ -4398,7 +4401,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Added by request: MoTeC ignition advance vs Load_kW with SD-only uncertainty and autoscale on Y.</t>
+          <t>Added by request: MoTeC ignition advance vs Load_kW with SD-only uncertainty and autoscale on Y. Y ticks: 1 deg autoscale.</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\_tmp_nanum_pipeline_28_remote_20260309\raw\PROCESSAR</t>
+          <t>C:\Users\SC61730\Downloads\raw_mestrado</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\_tmp_nanum_pipeline_28_remote_20260309\out</t>
+          <t>C:\Users\SC61730\Downloads\out_mestrado</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -1430,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4472,6 +4472,62 @@
       <c r="T45" t="inlineStr">
         <is>
           <t>Added by request: MoTeC fuel closed loop control bank 1 trim vs Load_kW with SD-only uncertainty and autoscale on Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ignition_delay_vs_upd_power_all.png</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ignition delay (abs) vs UPD measured power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>UPD_Power_Bin_kW</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ignition_Delay_abs_degCA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Potencia UPD medida (kW, bin 0.1)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ignition delay abs (deg CA)</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Added by request: abs(KIBOX_AI05_1 + Motec_Ignition Timing_mean_of_windows) with UPD power on X.</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -4519,6 +4519,18 @@
           <t>Ignition delay abs (deg CA)</t>
         </is>
       </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>55</v>
+      </c>
+      <c r="L46" t="n">
+        <v>5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
@@ -4527,7 +4539,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Added by request: abs(KIBOX_AI05_1 + Motec_Ignition Timing_mean_of_windows) with UPD power on X.</t>
+          <t>Added by request: abs(KIBOX_AI05_1 + Motec_Ignition Timing_mean_of_windows) with UPD power on X. | Y step set to 0.5 deg and X scale aligned with kibox (0..55 step 5).</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\raw_mestrado</t>
+          <t>C:\Users\SC61730\Downloads\raw_NANUM</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\out_mestrado</t>
+          <t>C:\Users\SC61730\Downloads\out_NANUM</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -1327,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\raw_NANUM</t>
+          <t>C:\Users\SC61730\Downloads\raw_mestrado\raw</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\out_NANUM</t>
+          <t>C:\Users\SC61730\Downloads\out_mestrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FUEL_DENSITY_KG_M3_D85B15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FUEL_DENSITY_KG_M3_E94H6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FUEL_DENSITY_KG_M3_E75H25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FUEL_DENSITY_KG_M3_E65H35</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FUEL_COST_R_L_D85B15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FUEL_COST_R_L_E94H6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FUEL_COST_R_L_E75H25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FUEL_COST_R_L_E65H35</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4540,6 +4596,146 @@
       <c r="T46" t="inlineStr">
         <is>
           <t>Added by request: abs(KIBOX_AI05_1 + Motec_Ignition Timing_mean_of_windows) with UPD power on X. | Y step set to 0.5 deg and X scale aligned with kibox (0..55 step 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>consumo_l_h_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Volumetric fuel flow vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Consumo_L_h</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>U_Consumo_L_h</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Fuel flow (L/h)</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>55</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Fuel volumetric flow from kg/h and density in Defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>custo_r_h_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fuel cost vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Custo_R_h</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>U_Custo_R_h</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Fuel cost (R$/h)</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>55</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Fuel hourly cost from volumetric flow and cost in Defaults</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="975" yWindow="240" windowWidth="21210" windowHeight="11295" tabRatio="600" firstSheet="3" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mappings" sheetId="1" state="visible" r:id="rId1"/>
@@ -1327,10 +1327,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="48.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="22" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1424,6 +1424,9 @@
           <t>FUEL_DENSITY_KG_M3_D85B15</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1431,6 +1434,9 @@
           <t>FUEL_DENSITY_KG_M3_E94H6</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>809</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1438,6 +1444,9 @@
           <t>FUEL_DENSITY_KG_M3_E75H25</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>873</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1445,6 +1454,9 @@
           <t>FUEL_DENSITY_KG_M3_E65H35</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>897</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1452,6 +1464,9 @@
           <t>FUEL_COST_R_L_D85B15</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1459,6 +1474,9 @@
           <t>FUEL_COST_R_L_E94H6</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1466,12 +1484,78 @@
           <t>FUEL_COST_R_L_E75H25</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>FUEL_COST_R_L_E65H35</t>
         </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MACHINE_HOURS_PER_YEAR_COLHEITADEIRA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MACHINE_DIESEL_L_H_COLHEITADEIRA</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MACHINE_HOURS_PER_YEAR_TRATOR_TRANSBORDO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MACHINE_DIESEL_L_H_TRATOR_TRANSBORDO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MACHINE_HOURS_PER_YEAR_CAMINHAO</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MACHINE_DIESEL_L_H_CAMINHAO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1486,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1675,7 +1759,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1745,7 +1829,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1810,7 +1894,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1875,7 +1959,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1940,7 +2024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2010,7 +2094,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2080,7 +2164,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2150,7 +2234,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2220,7 +2304,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2285,7 +2369,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2350,7 +2434,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2415,7 +2499,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2480,7 +2564,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2536,7 +2620,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2592,7 +2676,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2657,7 +2741,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2722,7 +2806,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2787,7 +2871,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2852,7 +2936,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2917,7 +3001,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2982,7 +3066,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3047,7 +3131,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3112,7 +3196,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3177,7 +3261,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3242,7 +3326,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3307,7 +3391,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3372,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3437,7 +3521,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3502,7 +3586,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3557,7 +3641,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3622,7 +3706,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3687,7 +3771,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3752,7 +3836,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3817,7 +3901,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3891,7 +3975,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -3961,7 +4045,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4035,7 +4119,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4179,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4160,7 +4244,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4230,7 +4314,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4300,7 +4384,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4379,7 +4463,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4452,7 +4536,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -4522,7 +4606,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>6,25,35</t>
+          <t>0,6,25,35</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4736,6 +4820,146 @@
       <c r="T48" t="inlineStr">
         <is>
           <t>Fuel hourly cost from volumetric flow and cost in Defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>economia_pct_vs_diesel_power_all.png</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hourly cost delta vs Diesel vs Power (negative = saving)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Economia_vs_Diesel_pct</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>U_Economia_vs_Diesel_pct</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cost delta vs Diesel (%)</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>55</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Signed hourly cost delta relative to diesel baseline. Negative values mean savings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>economia_r_h_vs_diesel_power_all.png</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Hourly cost delta vs Diesel vs Power (negative = saving)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Economia_vs_Diesel_R_h</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>U_Economia_vs_Diesel_R_h</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Cost delta vs Diesel (R$/h)</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>55</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Signed hourly cost delta relative to diesel baseline. Negative values mean savings.</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.28515625" customWidth="1" min="1" max="1"/>
@@ -621,44 +621,432 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T_CARTER_C</t>
+          <t>T_S_CIL_1_C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T_CARTER_mean_of_windows</t>
+          <t>T_S_CIL_1_mean_of_windows</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T_CARTER_sd_of_windows</t>
+          <t>T_S_CIL_1_sd_of_windows</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T_CARTER_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>T_CARTER_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>T_AMBIENTE_C</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>T_AMBIENTE_mean_of_windows</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>T_AMBIENTE_sd_of_windows</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>°C</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thermocouple type T + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Thermocouple type T + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>T_E_TURB_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>T_E_TURB_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T_S_TURB_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>T_S_TURB_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>?C</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Thermocouple type K + NI9213 selected mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P_E_TURB_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P_E_TURB_RAW_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P_E_TURB_RAW_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>kPa</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pressure sensor equipment uncertainty entered as +/-2.93 kPa via Instruments sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P_S_TURB_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P_S_TURB_RAW_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P_S_TURB_RAW_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>kPa</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pressure sensor equipment uncertainty entered as +/-2.93 kPa via Instruments sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P_COLETOR_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P_COLETOR_RAW_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P_COLETOR_RAW_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>kPa</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pressure sensor equipment uncertainty entered as +/-2.93 kPa via Instruments sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P_S_COMP_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P_S_COMP_RAW_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P_S_COMP_RAW_sd_of_windows</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>kPa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pressure sensor equipment uncertainty entered as +/-2.93 kPa via Instruments sheet.</t>
         </is>
       </c>
     </row>
@@ -673,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -751,6 +1139,16 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>setting_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>setting_value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -936,12 +1334,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>t_carter_c</t>
+          <t>T_S_CIL_1_C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TC_K_Class2_low</t>
+          <t>TC_K_ASTM_std_subzero</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,16 +1348,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-40</v>
+        <v>-200</v>
       </c>
       <c r="E6" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -972,24 +1370,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>IEC 60584 class 2 (example)</t>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>±2.5°C for -40..333°C</t>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>t_carter_c</t>
+          <t>T_S_CIL_1_C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TC_K_Class2_high</t>
+          <t>TC_K_ASTM_std_positive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -998,13 +1396,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1200</v>
+        <v>1372</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
         <v>0.0075</v>
@@ -1020,24 +1418,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>IEC 60584 class 2 (example)</t>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>±0.75% of reading for 333..1200°C</t>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>t_carter_c</t>
+          <t>T_S_CIL_1_C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NI9213_CJC_max</t>
+          <t>NI9213_K_HS_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1045,8 +1443,14 @@
           <t>rect</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1062,24 +1466,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NI 9213 (example placeholder)</t>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CJC contribution placeholder; replace with your datasheet spec</t>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>high_speed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T_AMBIENTE_C</t>
+          <t>T_S_CIL_1_C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TC_K_Class2_low</t>
+          <t>NI9213_K_HS_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1088,10 +1502,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>333</v>
+        <v>150</v>
       </c>
       <c r="F9" t="n">
         <v>2.5</v>
@@ -1110,24 +1524,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>IEC 60584 class 2 (example)</t>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>±2.5°C for -40..333°C</t>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>high_speed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T_AMBIENTE_C</t>
+          <t>T_S_CIL_1_C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TC_K_Class2_high</t>
+          <t>NI9213_K_HS_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1136,16 +1560,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>333</v>
+        <v>150</v>
       </c>
       <c r="E10" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0075</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1158,54 +1582,7800 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>IEC 60584 class 2 (example)</t>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>±0.75% of reading for 333..1200°C</t>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>high_speed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" t="n">
+        <v>900</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>900</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" t="n">
+        <v>500</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" t="n">
+        <v>900</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T_S_CIL_1_C</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>900</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>150</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>150</v>
+      </c>
+      <c r="E22" t="n">
+        <v>500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>500</v>
+      </c>
+      <c r="E23" t="n">
+        <v>900</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>900</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>150</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E27" t="n">
+        <v>500</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E28" t="n">
+        <v>900</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T_S_CIL_2_C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>900</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>150</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>150</v>
+      </c>
+      <c r="E34" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>500</v>
+      </c>
+      <c r="E35" t="n">
+        <v>900</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>900</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>150</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>150</v>
+      </c>
+      <c r="E39" t="n">
+        <v>500</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>500</v>
+      </c>
+      <c r="E40" t="n">
+        <v>900</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T_S_CIL_3_C</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>900</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>150</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E46" t="n">
+        <v>500</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>500</v>
+      </c>
+      <c r="E47" t="n">
+        <v>900</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>900</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>150</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>150</v>
+      </c>
+      <c r="E51" t="n">
+        <v>500</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>500</v>
+      </c>
+      <c r="E52" t="n">
+        <v>900</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T_S_CIL_4_C</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>900</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>150</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>150</v>
+      </c>
+      <c r="E58" t="n">
+        <v>500</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>500</v>
+      </c>
+      <c r="E59" t="n">
+        <v>900</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>900</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>150</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>150</v>
+      </c>
+      <c r="E63" t="n">
+        <v>500</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" t="n">
+        <v>900</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T_CARTER_C</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>900</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>150</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>150</v>
+      </c>
+      <c r="E70" t="n">
+        <v>500</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>500</v>
+      </c>
+      <c r="E71" t="n">
+        <v>900</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>900</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>150</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>150</v>
+      </c>
+      <c r="E75" t="n">
+        <v>500</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>500</v>
+      </c>
+      <c r="E76" t="n">
+        <v>900</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>T_RADIADOR_C</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>900</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>150</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>150</v>
+      </c>
+      <c r="E82" t="n">
+        <v>500</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>500</v>
+      </c>
+      <c r="E83" t="n">
+        <v>900</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>900</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F84" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>150</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>150</v>
+      </c>
+      <c r="E87" t="n">
+        <v>500</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>500</v>
+      </c>
+      <c r="E88" t="n">
+        <v>900</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T_S_AGUA_C</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>900</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>150</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>150</v>
+      </c>
+      <c r="E94" t="n">
+        <v>500</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>500</v>
+      </c>
+      <c r="E95" t="n">
+        <v>900</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>900</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>150</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>150</v>
+      </c>
+      <c r="E99" t="n">
+        <v>500</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>500</v>
+      </c>
+      <c r="E100" t="n">
+        <v>900</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>900</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>150</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>150</v>
+      </c>
+      <c r="E106" t="n">
+        <v>500</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>500</v>
+      </c>
+      <c r="E107" t="n">
+        <v>900</v>
+      </c>
+      <c r="F107" t="n">
+        <v>4</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>900</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>150</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>150</v>
+      </c>
+      <c r="E111" t="n">
+        <v>500</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>500</v>
+      </c>
+      <c r="E112" t="n">
+        <v>900</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>900</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?2% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TC_K_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1372</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Standard grade Type K: greater of ?2.2?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>150</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>150</v>
+      </c>
+      <c r="E118" t="n">
+        <v>500</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_4</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>500</v>
+      </c>
+      <c r="E119" t="n">
+        <v>900</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NI9213_K_HS_5</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>900</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F120" t="n">
+        <v>5</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>150</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>150</v>
+      </c>
+      <c r="E123" t="n">
+        <v>500</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_4</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>500</v>
+      </c>
+      <c r="E124" t="n">
+        <v>900</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NI9213_K_HR_5</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>900</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 3 (approx.)</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type K, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>T_AMBIENTE_C</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NI9213_CJC_max</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TC_T_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Standard grade Type T: greater of ?1.0?C or ?1.5% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TC_T_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>400</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Standard grade Type T: greater of ?1.0?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>200</v>
+      </c>
+      <c r="F129" t="n">
         <v>2.1</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>NI 9213 (example placeholder)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>CJC contribution placeholder; replace with your datasheet spec</t>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_3</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>200</v>
+      </c>
+      <c r="E130" t="n">
+        <v>600</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>600</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>200</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>200</v>
+      </c>
+      <c r="E134" t="n">
+        <v>600</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T_AMBIENTE_C</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>600</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TC_T_ASTM_std_subzero</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Standard grade Type T: greater of ?1.0?C or ?1.5% below 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TC_T_ASTM_std_positive</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>400</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>ASTM E230 / ANSI MC96.1 summary</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Standard grade Type T: greater of ?1.0?C or ?0.75% above 0?C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_1</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>4</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_2</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>200</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_3</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>200</v>
+      </c>
+      <c r="E140" t="n">
+        <v>600</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NI9213_T_HS_4</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>600</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-speed, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>200</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>200</v>
+      </c>
+      <c r="E144" t="n">
+        <v>600</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>T_WATERCOOLER_C</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>NI9213_T_HR_4</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>600</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>NI 9213 datasheet Fig. 4 (approx.)</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Approx. max module error for Type T, high-resolution, -40..70?C ambient. Includes CJC and module effects.</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>high_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>P_E_TURB_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PRESSURE_SENSOR_ABS_2p93_kPa</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>User input</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Sensor accuracy limit treated as rectangular distribution: +/-2.93 kPa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>P_S_TURB_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PRESSURE_SENSOR_ABS_2p93_kPa</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>User input</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Sensor accuracy limit treated as rectangular distribution: +/-2.93 kPa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>P_COLETOR_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PRESSURE_SENSOR_ABS_2p93_kPa</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>User input</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Sensor accuracy limit treated as rectangular distribution: +/-2.93 kPa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>P_S_COMP_RAW_kPa</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PRESSURE_SENSOR_ABS_2p93_kPa</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>User input</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Sensor accuracy limit treated as rectangular distribution: +/-2.93 kPa.</t>
         </is>
       </c>
     </row>
@@ -1327,7 +9497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1402,7 +9572,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\raw_mestrado\raw</t>
+          <t>C:\Users\SC61730\Downloads\raw_mestrado</t>
         </is>
       </c>
     </row>
@@ -1556,6 +9726,18 @@
       </c>
       <c r="B21" t="n">
         <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NI9213_TC_MODE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>high_speed</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +9752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1932,6 +10114,11 @@
           <t>DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>U_DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -1997,6 +10184,11 @@
           <t>DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>U_DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2067,6 +10259,11 @@
           <t>DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>U_DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2137,6 +10334,11 @@
           <t>DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>U_DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2207,6 +10409,11 @@
           <t>DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>U_DT_ADMISSAO_TO_T_E_CIL_AVG_C</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2472,6 +10679,11 @@
           <t>T_E_CIL_AVG_mean_of_windows</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>U_T_E_CIL_AVG_C</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2714,6 +10926,11 @@
           <t>P_E_TURB_RAW_mean_of_windows</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>U_P_E_TURB_RAW_KPA</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2779,6 +10996,11 @@
           <t>P_S_TURB_RAW_mean_of_windows</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>U_P_S_TURB_RAW_KPA</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2909,6 +11131,11 @@
           <t>P_S_COMP_RAW_mean_of_windows</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>U_P_S_COMP_RAW_KPA</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -2974,6 +11201,11 @@
           <t>P_COLETOR_RAW_mean_of_windows</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>U_P_COLETOR_RAW_KPA</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -3036,7 +11268,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>T_ADMISSÃO_mean_of_windows</t>
+          <t>T_ADMISSAO_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>U_T_ADMISSAO_C</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3104,6 +11341,11 @@
           <t>T_E_TURB_mean_of_windows</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>U_T_E_TURB_C</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -3169,6 +11411,11 @@
           <t>T_S_TURB_mean_of_windows</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>U_T_S_TURB_C</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -3364,6 +11611,11 @@
           <t>T_S_CIL_1_mean_of_windows</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>U_T_S_CIL_1_C</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -3429,6 +11681,11 @@
           <t>T_S_CIL_2_mean_of_windows</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>U_T_S_CIL_2_C</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -3494,6 +11751,11 @@
           <t>T_S_CIL_3_mean_of_windows</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>U_T_S_CIL_3_C</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -3559,6 +11821,11 @@
           <t>T_S_CIL_4_mean_of_windows</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>U_T_S_CIL_4_C</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -4083,6 +12350,11 @@
           <t>T_S_AGUA_mean_of_windows</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>U_T_S_AGUA_C</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Power (kW)</t>
@@ -4152,6 +12424,11 @@
           <t>T_WATERCOOLER_mean_of_windows</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>U_T_WATERCOOLER_C</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Power command (kW)</t>
@@ -4217,6 +12494,11 @@
           <t>T_RADIADOR_mean_of_windows</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>U_T_RADIADOR_C</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Power command (kW)</t>
@@ -4284,7 +12566,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>U_T_CARTER_C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4354,7 +12636,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>U_T_AMBIENTE_C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4960,6 +13242,198 @@
       <c r="T50" t="inlineStr">
         <is>
           <t>Signed hourly cost delta relative to diesel baseline. Negative values mean savings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>t_admissao_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Intake Temperature vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>T_ADMISSAO_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>U_T_ADMISSAO_C</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Intake temperature (?C)</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>55</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dedicated plot with propagated uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>t_e_turb_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Turbine Inlet Temperature vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>T_E_TURB_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>U_T_E_TURB_C</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Turbine inlet temperature (?C)</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>55</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dedicated plot with propagated uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>all_fuels_yx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>t_s_turb_vs_power_all.png</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Turbine Outlet Temperature vs Power (all fuels)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Load_kW</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>T_S_TURB_mean_of_windows</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>U_T_S_TURB_C</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Power (kW)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Turbine outlet temperature (?C)</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>55</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0,6,25,35</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dedicated plot with propagated uncertainty.</t>
         </is>
       </c>
     </row>

--- a/config/config_incertezas_rev3.xlsx
+++ b/config/config_incertezas_rev3.xlsx
@@ -9572,7 +9572,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\raw_mestrado</t>
+          <t>C:\Users\SC61730\Downloads\raw_wagnao</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C:\Users\SC61730\Downloads\out_mestrado</t>
+          <t>C:\Users\SC61730\Downloads\out_wagnao</t>
         </is>
       </c>
     </row>
